--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.36891138408353</v>
+        <v>5.422448099913574</v>
       </c>
       <c r="D2" t="n">
-        <v>32.57211678941137</v>
+        <v>5.292968978279348</v>
       </c>
       <c r="E2" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F2" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.8169307637874</v>
+        <v>5.820251249115453</v>
       </c>
       <c r="D3" t="n">
-        <v>36.42935975753811</v>
+        <v>5.919770960599942</v>
       </c>
       <c r="E3" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F3" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.09188136496739</v>
+        <v>2.289930721807201</v>
       </c>
       <c r="D4" t="n">
-        <v>13.67200701192189</v>
+        <v>2.221701139437307</v>
       </c>
       <c r="E4" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F4" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.8621229628056</v>
+        <v>2.90259498145591</v>
       </c>
       <c r="D5" t="n">
-        <v>18.57068231863164</v>
+        <v>3.017735876777641</v>
       </c>
       <c r="E5" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F5" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.21963441181459</v>
+        <v>8.648190591919871</v>
       </c>
       <c r="D6" t="n">
-        <v>52.07743847033915</v>
+        <v>8.462583751430113</v>
       </c>
       <c r="E6" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F6" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.30410582863681</v>
+        <v>6.711917197153482</v>
       </c>
       <c r="D7" t="n">
-        <v>40.34522108959226</v>
+        <v>6.556098427058742</v>
       </c>
       <c r="E7" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F7" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.73354691148626</v>
+        <v>7.594201373116518</v>
       </c>
       <c r="D8" t="n">
-        <v>47.98505187936941</v>
+        <v>7.797570930397529</v>
       </c>
       <c r="E8" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F8" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.68016329706768</v>
+        <v>6.285526535773498</v>
       </c>
       <c r="D9" t="n">
-        <v>39.94631116786532</v>
+        <v>6.491275564778114</v>
       </c>
       <c r="E9" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F9" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>60.22406386089646</v>
+        <v>9.786410377395676</v>
       </c>
       <c r="D10" t="n">
-        <v>61.50121343217123</v>
+        <v>9.993947182727826</v>
       </c>
       <c r="E10" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F10" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.33306576233992</v>
+        <v>5.254123186380237</v>
       </c>
       <c r="D11" t="n">
-        <v>33.14180424461447</v>
+        <v>5.385543189749852</v>
       </c>
       <c r="E11" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F11" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.6720800189215</v>
+        <v>7.421713003074744</v>
       </c>
       <c r="D12" t="n">
-        <v>46.81710585606012</v>
+        <v>7.607779701609769</v>
       </c>
       <c r="E12" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F12" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.62696812411483</v>
+        <v>6.764382320168661</v>
       </c>
       <c r="D13" t="n">
-        <v>42.63240351467645</v>
+        <v>6.927765571134924</v>
       </c>
       <c r="E13" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F13" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>57.23509308280511</v>
+        <v>9.300702625955831</v>
       </c>
       <c r="D14" t="n">
-        <v>58.43353533011189</v>
+        <v>9.495449491143184</v>
       </c>
       <c r="E14" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F14" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>47.70054631820491</v>
+        <v>7.751338776708297</v>
       </c>
       <c r="D15" t="n">
-        <v>48.50395105075759</v>
+        <v>7.881892045748108</v>
       </c>
       <c r="E15" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F15" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>60.74865571507387</v>
+        <v>9.871656553699506</v>
       </c>
       <c r="D16" t="n">
-        <v>61.48434547717569</v>
+        <v>9.991206140041051</v>
       </c>
       <c r="E16" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F16" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>75.58316396835433</v>
+        <v>12.28226414485758</v>
       </c>
       <c r="D17" t="n">
-        <v>76.64622715596558</v>
+        <v>12.45501191284441</v>
       </c>
       <c r="E17" t="n">
-        <v>15.33000974392492</v>
+        <v>2.491126583387799</v>
       </c>
       <c r="F17" t="n">
-        <v>15.60548610793487</v>
+        <v>2.535891492539416</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
